--- a/004_SapAriba_Target_Performer/lib/net45/Data/Config.xlsx
+++ b/004_SapAriba_Target_Performer/lib/net45/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grmusarpadev10\Desktop\Git_Upload_Sap\grm-usa-ar-ariba-performer\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Desktop\Linktera\Aniket\new target grm-usa-ar-ariba-performer.1.1.18\lib\net45\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D70B89-69D8-4678-A258-EE46FF02D900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D113DA-3389-4DDB-9CD0-324E4EA13523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="10815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="8745" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="141">
   <si>
     <t>Name</t>
   </si>
@@ -425,9 +425,6 @@
 RPA Robot.</t>
   </si>
   <si>
-    <t>-96</t>
-  </si>
-  <si>
     <t>BEXS0004</t>
   </si>
   <si>
@@ -458,6 +455,12 @@
   </si>
   <si>
     <t>When testTesting is true invoices are not submitted</t>
+  </si>
+  <si>
+    <t>-12</t>
+  </si>
+  <si>
+    <t>GMUSA_AR_CURRENTDATE_Target</t>
   </si>
 </sst>
 </file>
@@ -990,35 +993,32 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1026,14 +1026,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="59">
     <cellStyle name="Comma 2" xfId="38" xr:uid="{B0A0F9FC-9ADB-4FDF-AD5C-0A7345AEB1BA}"/>
@@ -1416,38 +1413,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -1479,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
@@ -1495,8 +1492,8 @@
       <c r="A8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>129</v>
+      <c r="B8" s="14" t="s">
+        <v>139</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>57</v>
@@ -1593,18 +1590,18 @@
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="16" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="16" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2736,10 +2733,10 @@
       <c r="A13" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="15" t="s">
+      <c r="B13" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2747,19 +2744,18 @@
       <c r="A14" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" s="15"/>
+      <c r="B14" s="21" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="17" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2781,7 +2777,7 @@
       <c r="A18" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2789,7 +2785,7 @@
       <c r="A19" t="s">
         <v>109</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" t="s">
         <v>110</v>
       </c>
     </row>
@@ -3902,7 +3898,7 @@
       <c r="A11" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="18" t="s">
         <v>111</v>
       </c>
       <c r="D11" t="s">
@@ -3913,7 +3909,7 @@
       <c r="A12" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="19" t="s">
         <v>118</v>
       </c>
       <c r="D12" t="s">
@@ -3946,7 +3942,7 @@
       <c r="A15" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="18" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3954,97 +3950,97 @@
       <c r="A16" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="18" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24" t="s">
+      <c r="C17" s="20"/>
+      <c r="D17" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E17" s="23" t="s">
+      <c r="E17" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24" t="s">
+      <c r="C18" s="20"/>
+      <c r="D18" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24" t="s">
+      <c r="C19" s="20"/>
+      <c r="D19" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="E19" s="12" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24" t="s">
+      <c r="C20" s="20"/>
+      <c r="D20" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="12" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24" t="s">
+      <c r="C21" s="20"/>
+      <c r="D21" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="23" t="s">
+      <c r="E21" s="12" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24" t="s">
+      <c r="C22" s="20"/>
+      <c r="D22" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="12" t="s">
         <v>105</v>
       </c>
     </row>
@@ -4064,7 +4060,14 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="25" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" t="s">
+        <v>140</v>
+      </c>
+    </row>
     <row r="26" spans="1:5" ht="14.25" customHeight="1"/>
     <row r="27" spans="1:5" ht="14.25" customHeight="1"/>
     <row r="28" spans="1:5" ht="14.25" customHeight="1"/>
@@ -5046,115 +5049,115 @@
   <dimension ref="A1:Z11"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="98" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="64" style="13" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="21.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="98" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="64" style="12" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="12" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:26" s="11" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
     </row>
     <row r="3" spans="1:26">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="30">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="30">
+      <c r="A6" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="30">
-      <c r="A6" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>134</v>
-      </c>
-    </row>
     <row r="7" spans="1:26">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:26">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:26">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:26">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="12" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:26">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="13" t="s">
         <v>127</v>
       </c>
     </row>
@@ -5228,23 +5231,23 @@
         <v>87</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:26">
-      <c r="A7" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="28" t="s">
+      <c r="A7" t="s">
         <v>136</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:26">

--- a/004_SapAriba_Target_Performer/lib/net45/Data/Config.xlsx
+++ b/004_SapAriba_Target_Performer/lib/net45/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Desktop\Linktera\Aniket\new target grm-usa-ar-ariba-performer.1.1.18\lib\net45\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D113DA-3389-4DDB-9CD0-324E4EA13523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B1D405-059A-45F5-8FC8-13E81BC4BBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="8745" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13425" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="140">
   <si>
     <t>Name</t>
   </si>
@@ -315,9 +315,6 @@
   </si>
   <si>
     <t>Mars_PDF_FilePath</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
   <si>
     <t>anita.kapur@accelirate.com</t>
@@ -1107,9 +1104,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1147,7 +1144,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1253,7 +1250,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1395,7 +1392,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1407,7 +1404,7 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
-    <col min="2" max="2" width="63" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="96.85546875" customWidth="1"/>
     <col min="3" max="3" width="81.42578125" customWidth="1"/>
     <col min="4" max="26" width="8.7109375" customWidth="1"/>
   </cols>
@@ -1476,7 +1473,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
@@ -1493,7 +1490,7 @@
         <v>69</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>57</v>
@@ -1526,16 +1523,16 @@
         <v>95</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" t="s">
         <v>124</v>
-      </c>
-      <c r="B12" t="s">
-        <v>125</v>
       </c>
       <c r="C12" s="2"/>
     </row>
@@ -1560,18 +1557,18 @@
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" t="s">
         <v>122</v>
-      </c>
-      <c r="C15" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>67</v>
@@ -2658,7 +2655,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -2734,7 +2731,7 @@
         <v>88</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
         <v>92</v>
@@ -2745,7 +2742,7 @@
         <v>89</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
@@ -2753,10 +2750,10 @@
         <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
@@ -2764,44 +2761,41 @@
         <v>91</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="16.899999999999999" customHeight="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="16.899999999999999" customHeight="1">
       <c r="B17" s="4"/>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="14.25" customHeight="1">
+    </row>
+    <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" t="s">
         <v>107</v>
       </c>
-      <c r="B18" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A19" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
         <v>109</v>
       </c>
-      <c r="B19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="22" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="23" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="24" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="25" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="26" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="27" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="28" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="29" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="30" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="31" spans="1:3" ht="14.25" customHeight="1"/>
-    <row r="32" spans="1:3" ht="14.25" customHeight="1"/>
+    </row>
+    <row r="20" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="21" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="22" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="23" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="24" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="25" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="26" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="27" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -3867,7 +3861,7 @@
         <v>66</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -3899,10 +3893,10 @@
         <v>79</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
@@ -3910,10 +3904,10 @@
         <v>80</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
@@ -3921,10 +3915,10 @@
         <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
@@ -3932,38 +3926,38 @@
         <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.25" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>74</v>
@@ -3971,14 +3965,14 @@
     </row>
     <row r="18" spans="1:5" ht="14.25" customHeight="1">
       <c r="A18" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>74</v>
@@ -3986,86 +3980,86 @@
     </row>
     <row r="19" spans="1:5" ht="14.25" customHeight="1">
       <c r="A19" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.25" customHeight="1">
       <c r="A20" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.25" customHeight="1">
       <c r="A21" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.25" customHeight="1">
       <c r="A22" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.25" customHeight="1">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="14.25" customHeight="1">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="14.25" customHeight="1"/>
@@ -5110,7 +5104,7 @@
         <v>49</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="30">
@@ -5118,7 +5112,7 @@
         <v>50</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:26">
@@ -5155,10 +5149,10 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>126</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -5231,23 +5225,23 @@
         <v>87</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:26">

--- a/004_SapAriba_Target_Performer/lib/net45/Data/Config.xlsx
+++ b/004_SapAriba_Target_Performer/lib/net45/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Desktop\Linktera\Aniket\new target grm-usa-ar-ariba-performer.1.1.18\lib\net45\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1UiPath\NA-Automation\USA-Target\004_SapAriba_Target_Performer\lib\net45\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B1D405-059A-45F5-8FC8-13E81BC4BBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1107EB04-92DD-40BC-BD99-1DB4D5AD2543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13425" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="8745" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -164,9 +164,6 @@
     <t>EXS0002</t>
   </si>
   <si>
-    <t>AR_Queue</t>
-  </si>
-  <si>
     <t>Login - Credentials for SAP Ariba Mars</t>
   </si>
   <si>
@@ -459,6 +456,9 @@
   <si>
     <t>GMUSA_AR_CURRENTDATE_Target</t>
   </si>
+  <si>
+    <t>GMUSAAR_MARS</t>
+  </si>
 </sst>
 </file>
 
@@ -469,7 +469,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="###,000"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -512,12 +512,6 @@
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="10"/>
@@ -863,134 +857,133 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="59">
+  <cellStyleXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="10" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="11" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="12" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="14" fillId="12" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="13" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="14" fillId="13" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="14" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="15" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="15" fillId="15" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="16" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="15" fillId="16" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="12" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="11" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="6" borderId="4" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="4" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="7" borderId="3" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="3" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="7" borderId="4" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="4" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1016,79 +1009,76 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="59">
-    <cellStyle name="Comma 2" xfId="38" xr:uid="{B0A0F9FC-9ADB-4FDF-AD5C-0A7345AEB1BA}"/>
-    <cellStyle name="Comma 3" xfId="39" xr:uid="{ABA8ACB6-0B11-4C3A-BDE3-DDC8C9514FB4}"/>
-    <cellStyle name="Currency 2" xfId="40" xr:uid="{A6FA0F0D-C4A5-4A16-B5B4-F85687BDC205}"/>
-    <cellStyle name="Currency 2 2" xfId="58" xr:uid="{35A9F480-71DC-4EB8-955F-FF7C21626247}"/>
-    <cellStyle name="Currency 2 3" xfId="57" xr:uid="{7C6CBCBC-D722-4142-BF30-9ED96A500F3F}"/>
-    <cellStyle name="Currency 3" xfId="41" xr:uid="{9A84016A-8881-457D-9377-4B6F32A16559}"/>
-    <cellStyle name="Currency 4" xfId="42" xr:uid="{681F22F5-A098-4A65-8173-005F1E2F55A5}"/>
-    <cellStyle name="Currency 5" xfId="43" xr:uid="{5B40BE57-E30B-4DAD-8A5C-44D3199BED9F}"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="58">
+    <cellStyle name="Comma 2" xfId="37" xr:uid="{B0A0F9FC-9ADB-4FDF-AD5C-0A7345AEB1BA}"/>
+    <cellStyle name="Comma 3" xfId="38" xr:uid="{ABA8ACB6-0B11-4C3A-BDE3-DDC8C9514FB4}"/>
+    <cellStyle name="Currency 2" xfId="39" xr:uid="{A6FA0F0D-C4A5-4A16-B5B4-F85687BDC205}"/>
+    <cellStyle name="Currency 2 2" xfId="57" xr:uid="{35A9F480-71DC-4EB8-955F-FF7C21626247}"/>
+    <cellStyle name="Currency 2 3" xfId="56" xr:uid="{7C6CBCBC-D722-4142-BF30-9ED96A500F3F}"/>
+    <cellStyle name="Currency 3" xfId="40" xr:uid="{9A84016A-8881-457D-9377-4B6F32A16559}"/>
+    <cellStyle name="Currency 4" xfId="41" xr:uid="{681F22F5-A098-4A65-8173-005F1E2F55A5}"/>
+    <cellStyle name="Currency 5" xfId="42" xr:uid="{5B40BE57-E30B-4DAD-8A5C-44D3199BED9F}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="44" xr:uid="{64F91263-06F7-40DC-9119-26BF1CB1AA37}"/>
-    <cellStyle name="Normal 11" xfId="45" xr:uid="{66C065EE-E7CE-4041-879F-475628CAE7C5}"/>
-    <cellStyle name="Normal 12" xfId="46" xr:uid="{F0E3F4EA-E777-4C9C-AB8E-EFDF9A1B319A}"/>
-    <cellStyle name="Normal 2" xfId="47" xr:uid="{FB89D73A-411A-4FAF-A969-501751EE8A9A}"/>
-    <cellStyle name="Normal 3" xfId="48" xr:uid="{71B00282-AB21-413A-801D-C4EF0C012938}"/>
-    <cellStyle name="Normal 4" xfId="49" xr:uid="{70FF5F6F-4445-4B3C-AEC0-538BA0CDC79E}"/>
-    <cellStyle name="Normal 4 2" xfId="50" xr:uid="{990BA0D0-1C73-470E-AC95-97C3D247F0D0}"/>
-    <cellStyle name="Normal 5" xfId="51" xr:uid="{A60F81E5-39A2-4FD7-8A90-EEFB47CF1C75}"/>
-    <cellStyle name="Normal 5 2" xfId="52" xr:uid="{30334450-B72E-4C90-A3EA-501BFFE8F197}"/>
-    <cellStyle name="Normal 6" xfId="53" xr:uid="{50CA88FE-9770-4F24-840D-1539C90E4B7A}"/>
-    <cellStyle name="Normal 7" xfId="54" xr:uid="{1C89AD30-6344-49E7-A0FB-FEC8E0DD1AF0}"/>
-    <cellStyle name="Normal 8" xfId="55" xr:uid="{2552C9DC-655F-4936-ADF8-F0C2C7D6976A}"/>
-    <cellStyle name="Normal 9" xfId="56" xr:uid="{449057E0-0018-4EC9-B428-D18353735683}"/>
-    <cellStyle name="SAPBorder" xfId="20" xr:uid="{1F25D168-0155-40B3-BA53-F6D427577145}"/>
-    <cellStyle name="SAPDataCell" xfId="3" xr:uid="{0203E604-DA0F-4264-9623-F10CF83D35FF}"/>
-    <cellStyle name="SAPDataTotalCell" xfId="4" xr:uid="{681DEE7B-E43C-4989-84CD-1B9BDBE23F59}"/>
-    <cellStyle name="SAPDimensionCell" xfId="2" xr:uid="{70AEF4BC-F76A-4ECB-90A3-A81B3ED25B74}"/>
-    <cellStyle name="SAPEditableDataCell" xfId="5" xr:uid="{A58F00FC-5BAC-446B-B071-65146338C013}"/>
-    <cellStyle name="SAPEditableDataTotalCell" xfId="8" xr:uid="{3CA6EAE7-2BA4-4C54-85B9-4F5231283DC2}"/>
-    <cellStyle name="SAPEmphasized" xfId="28" xr:uid="{19A39BBA-54FB-4D2C-8F3A-62A31A668880}"/>
-    <cellStyle name="SAPEmphasizedEditableDataCell" xfId="30" xr:uid="{6B1DB6D9-C409-40EF-88F0-89867B6A0244}"/>
-    <cellStyle name="SAPEmphasizedEditableDataTotalCell" xfId="31" xr:uid="{3986D1F7-0DA7-4996-9E08-389DA55DC5F9}"/>
-    <cellStyle name="SAPEmphasizedLockedDataCell" xfId="34" xr:uid="{8F69B2D0-6033-4CF8-8672-DF98637B8242}"/>
-    <cellStyle name="SAPEmphasizedLockedDataTotalCell" xfId="35" xr:uid="{296B9478-ED3A-48C0-9D25-25C134221B8D}"/>
-    <cellStyle name="SAPEmphasizedReadonlyDataCell" xfId="32" xr:uid="{374CBBFB-52F3-4D30-8F46-EE9DA721A7D6}"/>
-    <cellStyle name="SAPEmphasizedReadonlyDataTotalCell" xfId="33" xr:uid="{B6BFCAF1-599E-4CEC-B526-CF20A6137E12}"/>
-    <cellStyle name="SAPEmphasizedTotal" xfId="29" xr:uid="{AD90BA64-BADB-4DC3-8C8B-F8F8B1A89F59}"/>
-    <cellStyle name="SAPExceptionLevel1" xfId="11" xr:uid="{5A1745C1-562A-4184-9BF7-30020B96FA77}"/>
-    <cellStyle name="SAPExceptionLevel2" xfId="12" xr:uid="{CEFABF42-5DF1-46BB-A31B-76B39DDAB160}"/>
-    <cellStyle name="SAPExceptionLevel3" xfId="13" xr:uid="{9BE5B8B0-ABD6-4CAF-9A68-5408E86EA4CB}"/>
-    <cellStyle name="SAPExceptionLevel4" xfId="14" xr:uid="{3E6AD979-1D8E-4604-B795-FC7406D249E4}"/>
-    <cellStyle name="SAPExceptionLevel5" xfId="15" xr:uid="{0DD17BDD-7284-49BC-A45E-418DF6D4D02E}"/>
-    <cellStyle name="SAPExceptionLevel6" xfId="16" xr:uid="{E98F17A4-F6F0-416B-8A15-BD9ECCCB1816}"/>
-    <cellStyle name="SAPExceptionLevel7" xfId="17" xr:uid="{8A0C7010-0AB6-4E5E-A8BB-6D83D325FC21}"/>
-    <cellStyle name="SAPExceptionLevel8" xfId="18" xr:uid="{E74B1AFC-FAC9-424C-AD6C-B802D6D18F06}"/>
-    <cellStyle name="SAPExceptionLevel9" xfId="19" xr:uid="{B9B837DA-6C84-45E6-BBDE-DF44D4EC9664}"/>
-    <cellStyle name="SAPFormula" xfId="37" xr:uid="{7767B576-D41E-4A48-AEBE-8A4860263AE3}"/>
-    <cellStyle name="SAPHierarchyCell0" xfId="23" xr:uid="{C3245A14-773A-4A01-AB68-F461F5A34BAE}"/>
-    <cellStyle name="SAPHierarchyCell1" xfId="24" xr:uid="{D083AA4D-EBEC-4E3F-9046-994559B60A91}"/>
-    <cellStyle name="SAPHierarchyCell2" xfId="25" xr:uid="{BA258DF0-9775-4E3F-9DB9-3903D6D149AB}"/>
-    <cellStyle name="SAPHierarchyCell3" xfId="26" xr:uid="{14EA813D-9A48-44CC-A9FE-2995B9CF4177}"/>
-    <cellStyle name="SAPHierarchyCell4" xfId="27" xr:uid="{F3F46E0D-0A91-40D7-AC30-DD37B73D8D25}"/>
-    <cellStyle name="SAPLockedDataCell" xfId="7" xr:uid="{CF5A4714-52A0-4068-8BC5-2840AFB5F39C}"/>
-    <cellStyle name="SAPLockedDataTotalCell" xfId="10" xr:uid="{357CCCCA-3B4B-4FFC-A056-51265B3D319F}"/>
-    <cellStyle name="SAPMemberCell" xfId="21" xr:uid="{4C0C8BF7-53F2-42C0-B4E2-1E14770064C6}"/>
-    <cellStyle name="SAPMemberTotalCell" xfId="22" xr:uid="{BA64316D-9853-493B-8C49-C292E3E4CD6A}"/>
-    <cellStyle name="SAPMessageText" xfId="36" xr:uid="{5D852FA3-E38C-41D6-A3F8-E851B3E38BBA}"/>
-    <cellStyle name="SAPReadonlyDataCell" xfId="6" xr:uid="{601A3FB3-A997-419C-8E34-F855ACA4EE6D}"/>
-    <cellStyle name="SAPReadonlyDataTotalCell" xfId="9" xr:uid="{D572C95A-7177-4481-B153-D9CD4B56D7EE}"/>
+    <cellStyle name="Normal 10" xfId="43" xr:uid="{64F91263-06F7-40DC-9119-26BF1CB1AA37}"/>
+    <cellStyle name="Normal 11" xfId="44" xr:uid="{66C065EE-E7CE-4041-879F-475628CAE7C5}"/>
+    <cellStyle name="Normal 12" xfId="45" xr:uid="{F0E3F4EA-E777-4C9C-AB8E-EFDF9A1B319A}"/>
+    <cellStyle name="Normal 2" xfId="46" xr:uid="{FB89D73A-411A-4FAF-A969-501751EE8A9A}"/>
+    <cellStyle name="Normal 3" xfId="47" xr:uid="{71B00282-AB21-413A-801D-C4EF0C012938}"/>
+    <cellStyle name="Normal 4" xfId="48" xr:uid="{70FF5F6F-4445-4B3C-AEC0-538BA0CDC79E}"/>
+    <cellStyle name="Normal 4 2" xfId="49" xr:uid="{990BA0D0-1C73-470E-AC95-97C3D247F0D0}"/>
+    <cellStyle name="Normal 5" xfId="50" xr:uid="{A60F81E5-39A2-4FD7-8A90-EEFB47CF1C75}"/>
+    <cellStyle name="Normal 5 2" xfId="51" xr:uid="{30334450-B72E-4C90-A3EA-501BFFE8F197}"/>
+    <cellStyle name="Normal 6" xfId="52" xr:uid="{50CA88FE-9770-4F24-840D-1539C90E4B7A}"/>
+    <cellStyle name="Normal 7" xfId="53" xr:uid="{1C89AD30-6344-49E7-A0FB-FEC8E0DD1AF0}"/>
+    <cellStyle name="Normal 8" xfId="54" xr:uid="{2552C9DC-655F-4936-ADF8-F0C2C7D6976A}"/>
+    <cellStyle name="Normal 9" xfId="55" xr:uid="{449057E0-0018-4EC9-B428-D18353735683}"/>
+    <cellStyle name="SAPBorder" xfId="19" xr:uid="{1F25D168-0155-40B3-BA53-F6D427577145}"/>
+    <cellStyle name="SAPDataCell" xfId="2" xr:uid="{0203E604-DA0F-4264-9623-F10CF83D35FF}"/>
+    <cellStyle name="SAPDataTotalCell" xfId="3" xr:uid="{681DEE7B-E43C-4989-84CD-1B9BDBE23F59}"/>
+    <cellStyle name="SAPDimensionCell" xfId="1" xr:uid="{70AEF4BC-F76A-4ECB-90A3-A81B3ED25B74}"/>
+    <cellStyle name="SAPEditableDataCell" xfId="4" xr:uid="{A58F00FC-5BAC-446B-B071-65146338C013}"/>
+    <cellStyle name="SAPEditableDataTotalCell" xfId="7" xr:uid="{3CA6EAE7-2BA4-4C54-85B9-4F5231283DC2}"/>
+    <cellStyle name="SAPEmphasized" xfId="27" xr:uid="{19A39BBA-54FB-4D2C-8F3A-62A31A668880}"/>
+    <cellStyle name="SAPEmphasizedEditableDataCell" xfId="29" xr:uid="{6B1DB6D9-C409-40EF-88F0-89867B6A0244}"/>
+    <cellStyle name="SAPEmphasizedEditableDataTotalCell" xfId="30" xr:uid="{3986D1F7-0DA7-4996-9E08-389DA55DC5F9}"/>
+    <cellStyle name="SAPEmphasizedLockedDataCell" xfId="33" xr:uid="{8F69B2D0-6033-4CF8-8672-DF98637B8242}"/>
+    <cellStyle name="SAPEmphasizedLockedDataTotalCell" xfId="34" xr:uid="{296B9478-ED3A-48C0-9D25-25C134221B8D}"/>
+    <cellStyle name="SAPEmphasizedReadonlyDataCell" xfId="31" xr:uid="{374CBBFB-52F3-4D30-8F46-EE9DA721A7D6}"/>
+    <cellStyle name="SAPEmphasizedReadonlyDataTotalCell" xfId="32" xr:uid="{B6BFCAF1-599E-4CEC-B526-CF20A6137E12}"/>
+    <cellStyle name="SAPEmphasizedTotal" xfId="28" xr:uid="{AD90BA64-BADB-4DC3-8C8B-F8F8B1A89F59}"/>
+    <cellStyle name="SAPExceptionLevel1" xfId="10" xr:uid="{5A1745C1-562A-4184-9BF7-30020B96FA77}"/>
+    <cellStyle name="SAPExceptionLevel2" xfId="11" xr:uid="{CEFABF42-5DF1-46BB-A31B-76B39DDAB160}"/>
+    <cellStyle name="SAPExceptionLevel3" xfId="12" xr:uid="{9BE5B8B0-ABD6-4CAF-9A68-5408E86EA4CB}"/>
+    <cellStyle name="SAPExceptionLevel4" xfId="13" xr:uid="{3E6AD979-1D8E-4604-B795-FC7406D249E4}"/>
+    <cellStyle name="SAPExceptionLevel5" xfId="14" xr:uid="{0DD17BDD-7284-49BC-A45E-418DF6D4D02E}"/>
+    <cellStyle name="SAPExceptionLevel6" xfId="15" xr:uid="{E98F17A4-F6F0-416B-8A15-BD9ECCCB1816}"/>
+    <cellStyle name="SAPExceptionLevel7" xfId="16" xr:uid="{8A0C7010-0AB6-4E5E-A8BB-6D83D325FC21}"/>
+    <cellStyle name="SAPExceptionLevel8" xfId="17" xr:uid="{E74B1AFC-FAC9-424C-AD6C-B802D6D18F06}"/>
+    <cellStyle name="SAPExceptionLevel9" xfId="18" xr:uid="{B9B837DA-6C84-45E6-BBDE-DF44D4EC9664}"/>
+    <cellStyle name="SAPFormula" xfId="36" xr:uid="{7767B576-D41E-4A48-AEBE-8A4860263AE3}"/>
+    <cellStyle name="SAPHierarchyCell0" xfId="22" xr:uid="{C3245A14-773A-4A01-AB68-F461F5A34BAE}"/>
+    <cellStyle name="SAPHierarchyCell1" xfId="23" xr:uid="{D083AA4D-EBEC-4E3F-9046-994559B60A91}"/>
+    <cellStyle name="SAPHierarchyCell2" xfId="24" xr:uid="{BA258DF0-9775-4E3F-9DB9-3903D6D149AB}"/>
+    <cellStyle name="SAPHierarchyCell3" xfId="25" xr:uid="{14EA813D-9A48-44CC-A9FE-2995B9CF4177}"/>
+    <cellStyle name="SAPHierarchyCell4" xfId="26" xr:uid="{F3F46E0D-0A91-40D7-AC30-DD37B73D8D25}"/>
+    <cellStyle name="SAPLockedDataCell" xfId="6" xr:uid="{CF5A4714-52A0-4068-8BC5-2840AFB5F39C}"/>
+    <cellStyle name="SAPLockedDataTotalCell" xfId="9" xr:uid="{357CCCCA-3B4B-4FFC-A056-51265B3D319F}"/>
+    <cellStyle name="SAPMemberCell" xfId="20" xr:uid="{4C0C8BF7-53F2-42C0-B4E2-1E14770064C6}"/>
+    <cellStyle name="SAPMemberTotalCell" xfId="21" xr:uid="{BA64316D-9853-493B-8C49-C292E3E4CD6A}"/>
+    <cellStyle name="SAPMessageText" xfId="35" xr:uid="{5D852FA3-E38C-41D6-A3F8-E851B3E38BBA}"/>
+    <cellStyle name="SAPReadonlyDataCell" xfId="5" xr:uid="{601A3FB3-A997-419C-8E34-F855ACA4EE6D}"/>
+    <cellStyle name="SAPReadonlyDataTotalCell" xfId="8" xr:uid="{D572C95A-7177-4481-B153-D9CD4B56D7EE}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1448,7 +1438,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -1473,7 +1463,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
@@ -1487,125 +1477,122 @@
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" t="s">
         <v>123</v>
-      </c>
-      <c r="B12" t="s">
-        <v>124</v>
       </c>
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
         <v>70</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" t="s">
         <v>121</v>
-      </c>
-      <c r="C15" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1">
       <c r="A18" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>83</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1">
       <c r="A19" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="14.25" customHeight="1">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-    </row>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="21" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="22" spans="1:3" ht="14.25" customHeight="1"/>
     <row r="23" spans="1:3" ht="14.25" customHeight="1"/>
@@ -2655,7 +2642,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -2728,40 +2715,40 @@
     <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>133</v>
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
+        <v>132</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>136</v>
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="17" t="s">
         <v>96</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16.899999999999999" customHeight="1">
@@ -2769,18 +2756,18 @@
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" t="s">
         <v>106</v>
-      </c>
-      <c r="B18" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
         <v>108</v>
-      </c>
-      <c r="B19" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1"/>
@@ -3754,19 +3741,14 @@
     <row r="988" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
-  <hyperlinks>
-    <hyperlink ref="C15" r:id="rId1" xr:uid="{171D987C-ECDA-48E2-B05E-15A150050EE0}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{4B19CD85-1219-49D7-8B8F-DB99CC3C2101}"/>
-    <hyperlink ref="B13" r:id="rId3" xr:uid="{4171441C-6A9F-4F38-9E32-79CEEB4FCD9A}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z994"/>
+  <dimension ref="A1:Z993"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="42.42578125" bestFit="1" customWidth="1"/>
@@ -3858,208 +3840,208 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>110</v>
+        <v>78</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>117</v>
+        <v>79</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A17" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A18" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A19" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A20" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A21" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A22" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A17" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20" t="s">
+      <c r="B22" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="E17" s="12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A18" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A19" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A20" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A21" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A22" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20" t="s">
-        <v>119</v>
-      </c>
       <c r="E22" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.25" customHeight="1">
       <c r="A24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="14.25" customHeight="1">
       <c r="A25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="14.25" customHeight="1"/>
@@ -5030,7 +5012,6 @@
     <row r="991" ht="14.25" customHeight="1"/>
     <row r="992" ht="14.25" customHeight="1"/>
     <row r="993" ht="14.25" customHeight="1"/>
-    <row r="994" ht="14.25" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5096,63 +5077,63 @@
         <v>44</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="30">
       <c r="A5" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>131</v>
+        <v>48</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="30">
       <c r="A6" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>132</v>
+        <v>49</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>53</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>55</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>93</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>125</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -5206,42 +5187,42 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:26">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:26">
